--- a/Plan/Table/LiveData/08.ShopItemData.xlsx
+++ b/Plan/Table/LiveData/08.ShopItemData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\LiveData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C96272E0-1127-41B7-AD37-24C2BF6BD4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F41E756-F851-4C7E-AAE0-598B31B12E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{EA9AF9DF-3609-48D8-9DE3-1917E9195ED1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{4E24741F-650D-40FA-BB4C-D73C57317CF0}"/>
   </bookViews>
   <sheets>
     <sheet name="08.ShopItemData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Id</t>
   </si>
@@ -213,6 +213,30 @@
   </si>
   <si>
     <t>tra02</t>
+  </si>
+  <si>
+    <t>Card_Dummy_100</t>
+  </si>
+  <si>
+    <t>Card_Dummy_101</t>
+  </si>
+  <si>
+    <t>Card_Dummy_200</t>
+  </si>
+  <si>
+    <t>Card_Dummy_201</t>
+  </si>
+  <si>
+    <t>Card_Dummy_300</t>
+  </si>
+  <si>
+    <t>Card_Dummy_301</t>
+  </si>
+  <si>
+    <t>Card_Dummy_400</t>
+  </si>
+  <si>
+    <t>Card_Dummy_401</t>
   </si>
 </sst>
 </file>
@@ -595,9 +619,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CB3489-5F34-487A-8E59-3C43D8D0EB50}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{857B747E-C99C-4B35-B75B-230BC53EA27F}">
+  <dimension ref="A1:E62"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1518,6 +1541,142 @@
         <v>25</v>
       </c>
     </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>58</v>
+      </c>
+      <c r="D55">
+        <v>15</v>
+      </c>
+      <c r="E55">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>59</v>
+      </c>
+      <c r="D56">
+        <v>20</v>
+      </c>
+      <c r="E56">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>60</v>
+      </c>
+      <c r="D57">
+        <v>8</v>
+      </c>
+      <c r="E57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>61</v>
+      </c>
+      <c r="D58">
+        <v>13</v>
+      </c>
+      <c r="E58">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>62</v>
+      </c>
+      <c r="D59">
+        <v>15</v>
+      </c>
+      <c r="E59">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>63</v>
+      </c>
+      <c r="D60">
+        <v>20</v>
+      </c>
+      <c r="E60">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>64</v>
+      </c>
+      <c r="D61">
+        <v>15</v>
+      </c>
+      <c r="E61">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62">
+        <v>20</v>
+      </c>
+      <c r="E62">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
